--- a/test-data/ExcelData.xlsx
+++ b/test-data/ExcelData.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="286">
   <si>
     <t>Lakshmisri</t>
   </si>
@@ -886,6 +886,12 @@
   </si>
   <si>
     <t>success</t>
+  </si>
+  <si>
+    <t>valid email</t>
+  </si>
+  <si>
+    <t>*/*/*/</t>
   </si>
 </sst>
 </file>
@@ -1448,6 +1454,7 @@
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
     <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1509,11 +1516,11 @@
       <c r="A6" t="s">
         <v>212</v>
       </c>
-      <c r="B6">
-        <v>23</v>
+      <c r="B6" t="s">
+        <v>285</v>
       </c>
       <c r="C6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1524,7 +1531,7 @@
         <v>214</v>
       </c>
       <c r="C7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1535,7 +1542,7 @@
         <v>215</v>
       </c>
       <c r="C8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1546,7 +1553,7 @@
         <v>266</v>
       </c>
       <c r="C9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -1559,6 +1566,7 @@
     <hyperlink ref="B3" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 

--- a/test-data/ExcelData.xlsx
+++ b/test-data/ExcelData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23280" windowHeight="7860" tabRatio="888"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23280" windowHeight="7860" tabRatio="888" firstSheet="6" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="292">
   <si>
     <t>Lakshmisri</t>
   </si>
@@ -579,9 +579,6 @@
     <t>250</t>
   </si>
   <si>
-    <t>HR Request Type</t>
-  </si>
-  <si>
     <t>Address Change</t>
   </si>
   <si>
@@ -892,6 +889,27 @@
   </si>
   <si>
     <t>*/*/*/</t>
+  </si>
+  <si>
+    <t>requestType</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Update the Address</t>
+  </si>
+  <si>
+    <t>Update the Payroll Details</t>
+  </si>
+  <si>
+    <t>Other details</t>
+  </si>
+  <si>
+    <t>I request for the salary advance</t>
+  </si>
+  <si>
+    <t>Please send me the employment letter</t>
   </si>
 </sst>
 </file>
@@ -1459,13 +1477,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>279</v>
-      </c>
       <c r="C1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1473,21 +1491,21 @@
         <v>8</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="25" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1498,7 +1516,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1506,54 +1524,54 @@
         <v>10</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -1888,44 +1906,64 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="B1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>186</v>
+      <c r="B6" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1942,24 +1980,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" t="s">
         <v>187</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>188</v>
-      </c>
-      <c r="C1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" t="s">
         <v>190</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>191</v>
-      </c>
-      <c r="C2" t="s">
-        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -1980,30 +2018,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="C1" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>195</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2065,7 @@
         <v>135</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>137</v>
@@ -2044,7 +2082,7 @@
         <v>141</v>
       </c>
       <c r="C2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>140</v>
@@ -2071,7 +2109,7 @@
         <v>135</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>137</v>
@@ -2088,7 +2126,7 @@
         <v>141</v>
       </c>
       <c r="C2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>140</v>
@@ -2110,13 +2148,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B1" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>204</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2252,10 +2290,10 @@
         <v>32</v>
       </c>
       <c r="J1" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="K1" s="27" t="s">
         <v>217</v>
-      </c>
-      <c r="K1" s="27" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2454,12 +2492,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2479,18 +2517,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="C1" s="20" t="s">
         <v>273</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
@@ -2498,13 +2536,13 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B3" t="b">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -2533,7 +2571,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>76</v>
@@ -2571,7 +2609,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B2" t="s">
         <v>47</v>
@@ -2679,22 +2717,22 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B1" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="18" t="s">
-        <v>220</v>
-      </c>
       <c r="D1" s="18" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G1" s="18" t="s">
         <v>35</v>
@@ -2735,19 +2773,19 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F2" s="29">
         <v>10</v>
@@ -2771,7 +2809,7 @@
         <v>74</v>
       </c>
       <c r="M2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N2" t="s">
         <v>54</v>
@@ -2786,12 +2824,12 @@
         <v>86</v>
       </c>
       <c r="R2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B3" s="26">
         <v>20</v>
@@ -2800,13 +2838,13 @@
         <v>15</v>
       </c>
       <c r="D3" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="E3" t="s">
         <v>255</v>
       </c>
-      <c r="E3" t="s">
-        <v>256</v>
-      </c>
       <c r="F3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G3" t="s">
         <v>67</v>
@@ -2824,10 +2862,10 @@
         <v>59</v>
       </c>
       <c r="L3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N3" t="s">
         <v>62</v>
@@ -2847,7 +2885,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B4" s="15">
         <v>5</v>
@@ -2856,16 +2894,16 @@
         <v>5</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H4" t="s">
         <v>6</v>
@@ -2874,16 +2912,16 @@
         <v>66</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>52</v>
       </c>
       <c r="L4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="M4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N4" t="s">
         <v>54</v>
@@ -2903,7 +2941,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B5" s="26">
         <v>5</v>
@@ -2912,16 +2950,16 @@
         <v>5</v>
       </c>
       <c r="D5" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="E5" t="s">
         <v>255</v>
       </c>
-      <c r="E5" t="s">
-        <v>256</v>
-      </c>
       <c r="F5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H5" t="s">
         <v>68</v>
@@ -2930,16 +2968,16 @@
         <v>69</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>59</v>
       </c>
       <c r="L5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N5" t="s">
         <v>62</v>
@@ -2959,7 +2997,7 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B6" s="15">
         <v>20</v>
@@ -2968,16 +3006,16 @@
         <v>20</v>
       </c>
       <c r="D6" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="E6" t="s">
         <v>255</v>
       </c>
-      <c r="E6" t="s">
-        <v>256</v>
-      </c>
       <c r="F6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H6" t="s">
         <v>6</v>
@@ -2986,16 +3024,16 @@
         <v>66</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>52</v>
       </c>
       <c r="L6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N6" t="s">
         <v>54</v>
@@ -3015,7 +3053,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B7" s="15">
         <v>30</v>
@@ -3024,16 +3062,16 @@
         <v>30</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F7" s="29">
         <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H7" t="s">
         <v>6</v>
@@ -3042,16 +3080,16 @@
         <v>66</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K7" s="15" t="s">
         <v>52</v>
       </c>
       <c r="L7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N7" t="s">
         <v>54</v>
@@ -3066,12 +3104,12 @@
         <v>86</v>
       </c>
       <c r="R7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B8" s="26">
         <v>10</v>
@@ -3080,16 +3118,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="E8" t="s">
         <v>255</v>
       </c>
-      <c r="E8" t="s">
-        <v>256</v>
-      </c>
       <c r="F8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H8" t="s">
         <v>68</v>
@@ -3098,16 +3136,16 @@
         <v>69</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K8" s="15" t="s">
         <v>59</v>
       </c>
       <c r="L8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="M8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N8" t="s">
         <v>62</v>
@@ -3122,12 +3160,12 @@
         <v>87</v>
       </c>
       <c r="R8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B9" s="26">
         <v>25</v>
@@ -3136,16 +3174,16 @@
         <v>1</v>
       </c>
       <c r="D9" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="E9" t="s">
         <v>255</v>
       </c>
-      <c r="E9" t="s">
-        <v>256</v>
-      </c>
       <c r="F9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H9" t="s">
         <v>68</v>
@@ -3154,16 +3192,16 @@
         <v>69</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>59</v>
       </c>
       <c r="L9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N9" t="s">
         <v>62</v>
@@ -3178,7 +3216,7 @@
         <v>87</v>
       </c>
       <c r="R9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -3216,7 +3254,7 @@
         <v>36</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3227,7 +3265,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3243,7 +3281,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -3254,13 +3292,13 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -3305,7 +3343,7 @@
         <v>90</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3328,7 +3366,7 @@
         <v>97</v>
       </c>
       <c r="G2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H2" s="28">
         <v>45292</v>
@@ -3354,7 +3392,7 @@
         <v>97</v>
       </c>
       <c r="G3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H3" s="28">
         <v>45293</v>
@@ -3500,24 +3538,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="C1" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="E1" s="20" t="s">
         <v>260</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B2">
         <v>8</v>
@@ -3526,15 +3564,15 @@
         <v>10000</v>
       </c>
       <c r="D2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E2" t="s">
         <v>263</v>
-      </c>
-      <c r="E2" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -3543,15 +3581,15 @@
         <v>2000</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -3560,15 +3598,15 @@
         <v>3000</v>
       </c>
       <c r="D4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E4" t="s">
         <v>268</v>
-      </c>
-      <c r="E4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -3577,7 +3615,7 @@
         <v>500</v>
       </c>
       <c r="E5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
